--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-CRBIOChapitre.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-CRBIOChapitre.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-27T14:36:02+00:00</t>
+    <t>2025-06-05T15:38:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -247,6 +247,10 @@
     <t>Base</t>
   </si>
   <si>
+    <t xml:space="preserve">crbio-choice:La section doit contenir soit une ou plusieurs sous-sections CRBIOSousChapitre, soit une ou plusieurs entrées ResultatsExamensBiologieMedicale, mais pas les deux. {(choice.where(resolve() is CRBIOSousChapitre).exists() and not choice.where(resolve() is ResultatsExamensBiologieMedicale).exists()) or (not choice.where(resolve() is CRBIOSousChapitre).exists() and choice.where(resolve() is ResultatsExamensBiologieMedicale).exists())}
+</t>
+  </si>
+  <si>
     <t>CRBIOChapitre.codeSection</t>
   </si>
   <si>
@@ -292,21 +296,17 @@
     <t>CRBIOChapitre.sousSection</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/Section
-</t>
-  </si>
-  <si>
-    <t>Sous-sections</t>
-  </si>
-  <si>
-    <t>Section.sousSection</t>
-  </si>
-  <si>
-    <t>CRBIOChapitre.entree</t>
-  </si>
-  <si>
     <t xml:space="preserve">Base
 </t>
+  </si>
+  <si>
+    <t>Sous-sections</t>
+  </si>
+  <si>
+    <t>Section.sousSection</t>
+  </si>
+  <si>
+    <t>CRBIOChapitre.entree</t>
   </si>
   <si>
     <t>Entrées</t>
@@ -873,15 +873,15 @@
         <v>72</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>72</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -889,10 +889,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>72</v>
@@ -904,13 +904,13 @@
         <v>72</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -961,13 +961,13 @@
         <v>72</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>72</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -992,7 +992,7 @@
         <v>73</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>72</v>
@@ -1004,13 +1004,13 @@
         <v>72</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1061,13 +1061,13 @@
         <v>72</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>72</v>
@@ -1078,10 +1078,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1089,10 +1089,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>72</v>
@@ -1104,13 +1104,13 @@
         <v>72</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1161,13 +1161,13 @@
         <v>72</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>72</v>
@@ -1178,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1192,7 +1192,7 @@
         <v>73</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>72</v>
@@ -1204,13 +1204,13 @@
         <v>72</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1261,7 +1261,7 @@
         <v>72</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>73</v>
@@ -1278,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1292,7 +1292,7 @@
         <v>73</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>72</v>
@@ -1304,7 +1304,7 @@
         <v>72</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s" s="2">
         <v>96</v>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s" s="2">
         <v>74</v>
@@ -1464,7 +1464,7 @@
         <v>98</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AH8" t="s" s="2">
         <v>74</v>

--- a/htr-Corps-ModeleMetier/ig/StructureDefinition-CRBIOChapitre.xlsx
+++ b/htr-Corps-ModeleMetier/ig/StructureDefinition-CRBIOChapitre.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-05T15:38:56+00:00</t>
+    <t>2025-10-06T12:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
